--- a/data/phi_data_combined.xlsx
+++ b/data/phi_data_combined.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolinkilian/Desktop/Public Health Index/Github/Public-Health-Index/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9EBA601-663B-A24F-BD78-659776967093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6892E899-9132-2F45-BE74-C9E4B3C1B0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41300" yWindow="620" windowWidth="27340" windowHeight="20980" xr2:uid="{07406E1C-1769-574D-9B9C-B78BFD08E78B}"/>
+    <workbookView xWindow="39820" yWindow="8600" windowWidth="27340" windowHeight="20980" xr2:uid="{07406E1C-1769-574D-9B9C-B78BFD08E78B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,13 +138,7 @@
     <t>Physical activity</t>
   </si>
   <si>
-    <t>environment</t>
-  </si>
-  <si>
     <t>active societies</t>
-  </si>
-  <si>
-    <t>active environments</t>
   </si>
   <si>
     <t>active people</t>
@@ -204,16 +198,10 @@
     <t>control of marketing</t>
   </si>
   <si>
-    <t>social and environmental controls</t>
-  </si>
-  <si>
     <t>alcohol taxation</t>
   </si>
   <si>
     <t>maxvalue</t>
-  </si>
-  <si>
-    <t>price</t>
   </si>
   <si>
     <t>item_count</t>
@@ -253,6 +241,18 @@
   </si>
   <si>
     <t>sequential numbering for each item within policy domain and subscale</t>
+  </si>
+  <si>
+    <t>pricing</t>
+  </si>
+  <si>
+    <t>living environment</t>
+  </si>
+  <si>
+    <t>active living environments</t>
+  </si>
+  <si>
+    <t>social and living environmental controls</t>
   </si>
 </sst>
 </file>
@@ -659,10 +659,10 @@
         <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -673,7 +673,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -696,7 +696,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -719,7 +719,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -742,7 +742,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
@@ -765,7 +765,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -788,7 +788,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
@@ -811,7 +811,7 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -834,7 +834,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
@@ -857,7 +857,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -880,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -926,7 +926,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
@@ -949,7 +949,7 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
@@ -972,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
@@ -995,7 +995,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -1018,7 +1018,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
@@ -1041,7 +1041,7 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -1064,7 +1064,7 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
@@ -1087,7 +1087,7 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -1110,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -1133,7 +1133,7 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -1156,7 +1156,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -1179,7 +1179,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -1202,7 +1202,7 @@
         <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
@@ -1225,7 +1225,7 @@
         <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
@@ -1248,7 +1248,7 @@
         <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
@@ -1271,7 +1271,7 @@
         <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
@@ -1294,7 +1294,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
@@ -1317,7 +1317,7 @@
         <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
@@ -1340,7 +1340,7 @@
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
@@ -1363,7 +1363,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
@@ -1386,7 +1386,7 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
         <v>25</v>
@@ -1409,7 +1409,7 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D34" t="s">
         <v>25</v>
@@ -1432,7 +1432,7 @@
         <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D35" t="s">
         <v>25</v>
@@ -1455,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D36" t="s">
         <v>25</v>
@@ -1478,7 +1478,7 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>25</v>
@@ -1501,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
@@ -1524,7 +1524,7 @@
         <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
@@ -1547,7 +1547,7 @@
         <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
@@ -1570,7 +1570,7 @@
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
@@ -1593,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
@@ -1616,7 +1616,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -1639,7 +1639,7 @@
         <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
@@ -1662,7 +1662,7 @@
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
@@ -1685,7 +1685,7 @@
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
@@ -1708,7 +1708,7 @@
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
@@ -1731,7 +1731,7 @@
         <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
@@ -1754,7 +1754,7 @@
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
@@ -1777,7 +1777,7 @@
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
@@ -1800,7 +1800,7 @@
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
@@ -1823,7 +1823,7 @@
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
@@ -1846,7 +1846,7 @@
         <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
@@ -1869,7 +1869,7 @@
         <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
@@ -1892,7 +1892,7 @@
         <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
@@ -2329,7 +2329,7 @@
         <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D74" t="s">
         <v>29</v>
@@ -2352,7 +2352,7 @@
         <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D75" t="s">
         <v>29</v>
@@ -2375,7 +2375,7 @@
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
@@ -2398,7 +2398,7 @@
         <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
@@ -2421,7 +2421,7 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
@@ -2444,7 +2444,7 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
@@ -2467,7 +2467,7 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D80" t="s">
         <v>29</v>
@@ -2490,7 +2490,7 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
         <v>29</v>
@@ -2513,7 +2513,7 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D82" t="s">
         <v>29</v>
@@ -2536,7 +2536,7 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
@@ -2559,7 +2559,7 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D84" t="s">
         <v>29</v>
@@ -2582,7 +2582,7 @@
         <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
@@ -2605,7 +2605,7 @@
         <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
@@ -2628,7 +2628,7 @@
         <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D87" t="s">
         <v>29</v>
@@ -2651,7 +2651,7 @@
         <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D88" t="s">
         <v>29</v>
@@ -2674,7 +2674,7 @@
         <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
@@ -2697,7 +2697,7 @@
         <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D90" t="s">
         <v>29</v>
@@ -2720,7 +2720,7 @@
         <v>22</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D91" t="s">
         <v>29</v>
@@ -2743,7 +2743,7 @@
         <v>22</v>
       </c>
       <c r="C92" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D92" t="s">
         <v>30</v>
@@ -2766,7 +2766,7 @@
         <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D93" t="s">
         <v>30</v>
@@ -2789,7 +2789,7 @@
         <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
         <v>30</v>
@@ -2812,7 +2812,7 @@
         <v>22</v>
       </c>
       <c r="C95" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D95" t="s">
         <v>30</v>
@@ -2835,7 +2835,7 @@
         <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D96" t="s">
         <v>30</v>
@@ -2858,7 +2858,7 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D97" t="s">
         <v>30</v>
@@ -2881,7 +2881,7 @@
         <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D98" t="s">
         <v>30</v>
@@ -2904,7 +2904,7 @@
         <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D99" t="s">
         <v>30</v>
@@ -2927,7 +2927,7 @@
         <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D100" t="s">
         <v>30</v>
@@ -2950,7 +2950,7 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D101" t="s">
         <v>30</v>
@@ -2973,7 +2973,7 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D102" t="s">
         <v>30</v>
@@ -2996,7 +2996,7 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D103" t="s">
         <v>30</v>
@@ -3019,7 +3019,7 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D104" t="s">
         <v>30</v>
@@ -3042,7 +3042,7 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D105" t="s">
         <v>30</v>
@@ -3065,7 +3065,7 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D106" t="s">
         <v>30</v>
@@ -3088,7 +3088,7 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D107" t="s">
         <v>30</v>
@@ -3111,7 +3111,7 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D108" t="s">
         <v>30</v>
@@ -3134,7 +3134,7 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D109" t="s">
         <v>30</v>
@@ -3157,10 +3157,10 @@
         <v>31</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D110" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -3180,10 +3180,10 @@
         <v>31</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D111" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -3203,10 +3203,10 @@
         <v>31</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D112" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -3226,10 +3226,10 @@
         <v>31</v>
       </c>
       <c r="C113" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E113">
         <v>0.875</v>
@@ -3249,10 +3249,10 @@
         <v>31</v>
       </c>
       <c r="C114" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E114">
         <v>0.875</v>
@@ -3272,10 +3272,10 @@
         <v>31</v>
       </c>
       <c r="C115" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D115" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -3295,10 +3295,10 @@
         <v>31</v>
       </c>
       <c r="C116" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -3318,10 +3318,10 @@
         <v>31</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E117">
         <v>0.875</v>
@@ -3341,10 +3341,10 @@
         <v>31</v>
       </c>
       <c r="C118" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -3364,10 +3364,10 @@
         <v>31</v>
       </c>
       <c r="C119" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -3387,10 +3387,10 @@
         <v>31</v>
       </c>
       <c r="C120" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E120">
         <v>0.625</v>
@@ -3410,10 +3410,10 @@
         <v>31</v>
       </c>
       <c r="C121" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -3433,10 +3433,10 @@
         <v>31</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E122" s="2">
         <v>0.875</v>
@@ -3456,10 +3456,10 @@
         <v>31</v>
       </c>
       <c r="C123" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -3479,10 +3479,10 @@
         <v>31</v>
       </c>
       <c r="C124" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E124">
         <v>0.5</v>
@@ -3502,10 +3502,10 @@
         <v>31</v>
       </c>
       <c r="C125" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E125">
         <v>0.75</v>
@@ -3525,10 +3525,10 @@
         <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E126">
         <v>0.75</v>
@@ -3548,10 +3548,10 @@
         <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -3571,10 +3571,10 @@
         <v>31</v>
       </c>
       <c r="C128" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D128" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E128">
         <v>0.77500000000000002</v>
@@ -3594,10 +3594,10 @@
         <v>31</v>
       </c>
       <c r="C129" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D129" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E129">
         <v>0.97499999999999998</v>
@@ -3617,10 +3617,10 @@
         <v>31</v>
       </c>
       <c r="C130" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E130">
         <v>0.6</v>
@@ -3640,10 +3640,10 @@
         <v>31</v>
       </c>
       <c r="C131" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E131">
         <v>0.77500000000000002</v>
@@ -3663,10 +3663,10 @@
         <v>31</v>
       </c>
       <c r="C132" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D132" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E132">
         <v>0.97499999999999998</v>
@@ -3686,10 +3686,10 @@
         <v>31</v>
       </c>
       <c r="C133" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D133" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -3709,10 +3709,10 @@
         <v>31</v>
       </c>
       <c r="C134" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D134" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -3732,10 +3732,10 @@
         <v>31</v>
       </c>
       <c r="C135" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D135" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E135">
         <v>0.57499999999999996</v>
@@ -3755,10 +3755,10 @@
         <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D136" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E136">
         <v>0.97499999999999998</v>
@@ -3778,10 +3778,10 @@
         <v>31</v>
       </c>
       <c r="C137" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -3801,10 +3801,10 @@
         <v>31</v>
       </c>
       <c r="C138" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D138" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -3824,10 +3824,10 @@
         <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D139" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E139">
         <v>0.93330000000000002</v>
@@ -3847,10 +3847,10 @@
         <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D140" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -3870,10 +3870,10 @@
         <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D141" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -3893,10 +3893,10 @@
         <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D142" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -3916,10 +3916,10 @@
         <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D143" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E143">
         <v>0.57499999999999996</v>
@@ -3939,10 +3939,10 @@
         <v>31</v>
       </c>
       <c r="C144" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D144" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E144">
         <v>0.97499999999999998</v>
@@ -3962,10 +3962,10 @@
         <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D145" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E145">
         <v>0.97499999999999998</v>
@@ -3985,10 +3985,10 @@
         <v>31</v>
       </c>
       <c r="C146" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E146">
         <v>0.27779999999999999</v>
@@ -4008,10 +4008,10 @@
         <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D147" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4031,10 +4031,10 @@
         <v>31</v>
       </c>
       <c r="C148" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D148" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E148">
         <v>0.66669999999999996</v>
@@ -4054,10 +4054,10 @@
         <v>31</v>
       </c>
       <c r="C149" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D149" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E149">
         <v>0.77780000000000005</v>
@@ -4077,10 +4077,10 @@
         <v>31</v>
       </c>
       <c r="C150" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D150" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E150">
         <v>0.55559999999999998</v>
@@ -4100,10 +4100,10 @@
         <v>31</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D151" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E151">
         <v>0.88890000000000002</v>
@@ -4123,10 +4123,10 @@
         <v>31</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D152" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E152">
         <v>0.77780000000000005</v>
@@ -4146,10 +4146,10 @@
         <v>31</v>
       </c>
       <c r="C153" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D153" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E153">
         <v>0.55559999999999998</v>
@@ -4169,10 +4169,10 @@
         <v>31</v>
       </c>
       <c r="C154" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D154" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E154">
         <v>0.66669999999999996</v>
@@ -4192,10 +4192,10 @@
         <v>31</v>
       </c>
       <c r="C155" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D155" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E155">
         <v>0.66669999999999996</v>
@@ -4215,10 +4215,10 @@
         <v>31</v>
       </c>
       <c r="C156" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D156" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E156">
         <v>0.2278</v>
@@ -4238,10 +4238,10 @@
         <v>31</v>
       </c>
       <c r="C157" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E157">
         <v>0.77780000000000005</v>
@@ -4261,10 +4261,10 @@
         <v>31</v>
       </c>
       <c r="C158" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D158" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E158">
         <v>0.55559999999999998</v>
@@ -4284,10 +4284,10 @@
         <v>31</v>
       </c>
       <c r="C159" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D159" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E159">
         <v>0.66669999999999996</v>
@@ -4307,10 +4307,10 @@
         <v>31</v>
       </c>
       <c r="C160" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D160" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E160">
         <v>0.33329999999999999</v>
@@ -4330,10 +4330,10 @@
         <v>31</v>
       </c>
       <c r="C161" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D161" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E161">
         <v>0.5</v>
@@ -4353,10 +4353,10 @@
         <v>31</v>
       </c>
       <c r="C162" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D162" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E162">
         <v>0.5</v>
@@ -4376,10 +4376,10 @@
         <v>31</v>
       </c>
       <c r="C163" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D163" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E163">
         <v>0.88890000000000002</v>
@@ -4399,10 +4399,10 @@
         <v>31</v>
       </c>
       <c r="C164" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D164" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E164">
         <v>0.83330000000000004</v>
@@ -4422,10 +4422,10 @@
         <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D165" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E165">
         <v>0.83330000000000004</v>
@@ -4445,10 +4445,10 @@
         <v>31</v>
       </c>
       <c r="C166" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D166" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -4468,10 +4468,10 @@
         <v>31</v>
       </c>
       <c r="C167" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D167" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E167">
         <v>0.75</v>
@@ -4491,10 +4491,10 @@
         <v>31</v>
       </c>
       <c r="C168" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D168" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -4514,10 +4514,10 @@
         <v>31</v>
       </c>
       <c r="C169" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D169" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E169">
         <v>0.91669999999999996</v>
@@ -4537,10 +4537,10 @@
         <v>31</v>
       </c>
       <c r="C170" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D170" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E170">
         <v>0.83330000000000004</v>
@@ -4560,10 +4560,10 @@
         <v>31</v>
       </c>
       <c r="C171" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D171" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E171">
         <v>0.83330000000000004</v>
@@ -4583,10 +4583,10 @@
         <v>31</v>
       </c>
       <c r="C172" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D172" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -4606,10 +4606,10 @@
         <v>31</v>
       </c>
       <c r="C173" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D173" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E173">
         <v>0.83330000000000004</v>
@@ -4629,10 +4629,10 @@
         <v>31</v>
       </c>
       <c r="C174" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D174" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E174">
         <v>0.83330000000000004</v>
@@ -4652,10 +4652,10 @@
         <v>31</v>
       </c>
       <c r="C175" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D175" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -4675,10 +4675,10 @@
         <v>31</v>
       </c>
       <c r="C176" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D176" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E176">
         <v>0.86109999999999998</v>
@@ -4698,10 +4698,10 @@
         <v>31</v>
       </c>
       <c r="C177" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D177" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E177">
         <v>0.83330000000000004</v>
@@ -4721,10 +4721,10 @@
         <v>31</v>
       </c>
       <c r="C178" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D178" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E178">
         <v>0.83330000000000004</v>
@@ -4744,10 +4744,10 @@
         <v>31</v>
       </c>
       <c r="C179" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D179" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E179">
         <v>0.83330000000000004</v>
@@ -4767,10 +4767,10 @@
         <v>31</v>
       </c>
       <c r="C180" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D180" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E180">
         <v>0.58330000000000004</v>
@@ -4790,10 +4790,10 @@
         <v>31</v>
       </c>
       <c r="C181" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D181" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -4810,13 +4810,13 @@
         <v>4</v>
       </c>
       <c r="B182" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C182" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D182" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E182">
         <v>14</v>
@@ -4833,13 +4833,13 @@
         <v>5</v>
       </c>
       <c r="B183" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C183" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D183" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E183">
         <v>13</v>
@@ -4856,13 +4856,13 @@
         <v>6</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C184" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D184" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E184">
         <v>14</v>
@@ -4879,13 +4879,13 @@
         <v>7</v>
       </c>
       <c r="B185" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C185" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D185" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E185">
         <v>13</v>
@@ -4902,13 +4902,13 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C186" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D186" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E186">
         <v>17</v>
@@ -4925,13 +4925,13 @@
         <v>9</v>
       </c>
       <c r="B187" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C187" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D187" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E187">
         <v>21</v>
@@ -4948,13 +4948,13 @@
         <v>10</v>
       </c>
       <c r="B188" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C188" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D188" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E188">
         <v>27</v>
@@ -4971,13 +4971,13 @@
         <v>11</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C189" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D189" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E189">
         <v>12</v>
@@ -4994,13 +4994,13 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C190" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D190" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E190">
         <v>14</v>
@@ -5017,13 +5017,13 @@
         <v>13</v>
       </c>
       <c r="B191" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C191" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D191" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E191">
         <v>9</v>
@@ -5040,13 +5040,13 @@
         <v>14</v>
       </c>
       <c r="B192" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C192" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D192" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E192">
         <v>15</v>
@@ -5063,13 +5063,13 @@
         <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C193" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D193" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E193">
         <v>20</v>
@@ -5086,13 +5086,13 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C194" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D194" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E194">
         <v>11</v>
@@ -5109,13 +5109,13 @@
         <v>17</v>
       </c>
       <c r="B195" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C195" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D195" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E195">
         <v>14</v>
@@ -5132,13 +5132,13 @@
         <v>18</v>
       </c>
       <c r="B196" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C196" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D196" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E196">
         <v>11</v>
@@ -5155,13 +5155,13 @@
         <v>19</v>
       </c>
       <c r="B197" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C197" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D197" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E197">
         <v>12</v>
@@ -5178,13 +5178,13 @@
         <v>20</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C198" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D198" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E198">
         <v>13</v>
@@ -5201,13 +5201,13 @@
         <v>21</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C199" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D199" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E199">
         <v>27</v>
@@ -5224,13 +5224,13 @@
         <v>4</v>
       </c>
       <c r="B200" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C200" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D200" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E200">
         <v>16</v>
@@ -5247,13 +5247,13 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C201" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D201" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E201">
         <v>11</v>
@@ -5270,13 +5270,13 @@
         <v>6</v>
       </c>
       <c r="B202" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C202" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D202" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E202">
         <v>11</v>
@@ -5293,13 +5293,13 @@
         <v>7</v>
       </c>
       <c r="B203" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C203" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D203" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E203">
         <v>15</v>
@@ -5316,13 +5316,13 @@
         <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C204" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D204" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E204">
         <v>18</v>
@@ -5339,13 +5339,13 @@
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C205" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D205" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E205">
         <v>18</v>
@@ -5362,13 +5362,13 @@
         <v>10</v>
       </c>
       <c r="B206" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C206" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D206" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E206">
         <v>22</v>
@@ -5385,13 +5385,13 @@
         <v>11</v>
       </c>
       <c r="B207" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C207" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D207" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E207">
         <v>13</v>
@@ -5408,13 +5408,13 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C208" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D208" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5431,13 +5431,13 @@
         <v>13</v>
       </c>
       <c r="B209" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C209" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D209" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5454,13 +5454,13 @@
         <v>14</v>
       </c>
       <c r="B210" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C210" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D210" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E210">
         <v>21</v>
@@ -5477,13 +5477,13 @@
         <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C211" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D211" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E211">
         <v>17</v>
@@ -5500,13 +5500,13 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C212" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D212" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E212">
         <v>18</v>
@@ -5523,13 +5523,13 @@
         <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C213" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D213" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E213">
         <v>11</v>
@@ -5546,13 +5546,13 @@
         <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C214" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D214" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E214">
         <v>15</v>
@@ -5569,13 +5569,13 @@
         <v>19</v>
       </c>
       <c r="B215" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C215" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E215">
         <v>11</v>
@@ -5592,13 +5592,13 @@
         <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C216" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D216" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E216">
         <v>15</v>
@@ -5615,13 +5615,13 @@
         <v>21</v>
       </c>
       <c r="B217" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C217" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D217" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E217">
         <v>22</v>
@@ -5638,13 +5638,13 @@
         <v>4</v>
       </c>
       <c r="B218" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C218" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D218" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E218">
         <v>1</v>
@@ -5661,16 +5661,16 @@
         <v>5</v>
       </c>
       <c r="B219" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C219" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D219" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E219" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F219">
         <v>10</v>
@@ -5684,13 +5684,13 @@
         <v>6</v>
       </c>
       <c r="B220" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C220" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D220" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -5707,16 +5707,16 @@
         <v>7</v>
       </c>
       <c r="B221" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C221" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D221" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E221" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F221">
         <v>10</v>
@@ -5730,13 +5730,13 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C222" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D222" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E222">
         <v>2</v>
@@ -5753,13 +5753,13 @@
         <v>9</v>
       </c>
       <c r="B223" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C223" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D223" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E223">
         <v>3</v>
@@ -5776,13 +5776,13 @@
         <v>10</v>
       </c>
       <c r="B224" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C224" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D224" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -5799,16 +5799,16 @@
         <v>11</v>
       </c>
       <c r="B225" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C225" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D225" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E225" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F225">
         <v>10</v>
@@ -5822,13 +5822,13 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C226" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D226" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E226">
         <v>1</v>
@@ -5845,13 +5845,13 @@
         <v>13</v>
       </c>
       <c r="B227" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C227" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D227" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -5868,13 +5868,13 @@
         <v>14</v>
       </c>
       <c r="B228" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C228" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D228" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E228">
         <v>3</v>
@@ -5891,13 +5891,13 @@
         <v>15</v>
       </c>
       <c r="B229" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C229" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D229" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -5914,13 +5914,13 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C230" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D230" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -5937,13 +5937,13 @@
         <v>17</v>
       </c>
       <c r="B231" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C231" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D231" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -5960,13 +5960,13 @@
         <v>18</v>
       </c>
       <c r="B232" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C232" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D232" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -5983,13 +5983,13 @@
         <v>19</v>
       </c>
       <c r="B233" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C233" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D233" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E233">
         <v>1</v>
@@ -6006,13 +6006,13 @@
         <v>20</v>
       </c>
       <c r="B234" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C234" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D234" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -6029,16 +6029,16 @@
         <v>21</v>
       </c>
       <c r="B235" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C235" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D235" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F235">
         <v>10</v>
@@ -6052,13 +6052,13 @@
         <v>4</v>
       </c>
       <c r="B236" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C236" t="s">
         <v>27</v>
       </c>
       <c r="D236" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E236">
         <v>10</v>
@@ -6075,13 +6075,13 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C237" t="s">
         <v>27</v>
       </c>
       <c r="D237" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E237">
         <v>13</v>
@@ -6098,13 +6098,13 @@
         <v>6</v>
       </c>
       <c r="B238" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C238" t="s">
         <v>27</v>
       </c>
       <c r="D238" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E238">
         <v>6</v>
@@ -6121,13 +6121,13 @@
         <v>7</v>
       </c>
       <c r="B239" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C239" t="s">
         <v>27</v>
       </c>
       <c r="D239" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E239">
         <v>11</v>
@@ -6144,13 +6144,13 @@
         <v>8</v>
       </c>
       <c r="B240" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C240" t="s">
         <v>27</v>
       </c>
       <c r="D240" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E240">
         <v>13</v>
@@ -6167,13 +6167,13 @@
         <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C241" t="s">
         <v>27</v>
       </c>
       <c r="D241" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E241">
         <v>11</v>
@@ -6190,13 +6190,13 @@
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C242" t="s">
         <v>27</v>
       </c>
       <c r="D242" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E242">
         <v>13</v>
@@ -6213,13 +6213,13 @@
         <v>11</v>
       </c>
       <c r="B243" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C243" t="s">
         <v>27</v>
       </c>
       <c r="D243" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E243">
         <v>11</v>
@@ -6236,13 +6236,13 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C244" t="s">
         <v>27</v>
       </c>
       <c r="D244" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E244">
         <v>10</v>
@@ -6259,13 +6259,13 @@
         <v>13</v>
       </c>
       <c r="B245" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C245" t="s">
         <v>27</v>
       </c>
       <c r="D245" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E245">
         <v>9</v>
@@ -6282,13 +6282,13 @@
         <v>14</v>
       </c>
       <c r="B246" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C246" t="s">
         <v>27</v>
       </c>
       <c r="D246" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E246">
         <v>10</v>
@@ -6305,13 +6305,13 @@
         <v>15</v>
       </c>
       <c r="B247" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C247" t="s">
         <v>27</v>
       </c>
       <c r="D247" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E247">
         <v>13</v>
@@ -6328,13 +6328,13 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C248" t="s">
         <v>27</v>
       </c>
       <c r="D248" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E248">
         <v>7</v>
@@ -6351,13 +6351,13 @@
         <v>17</v>
       </c>
       <c r="B249" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C249" t="s">
         <v>27</v>
       </c>
       <c r="D249" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E249">
         <v>11</v>
@@ -6374,13 +6374,13 @@
         <v>18</v>
       </c>
       <c r="B250" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C250" t="s">
         <v>27</v>
       </c>
       <c r="D250" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E250">
         <v>9</v>
@@ -6397,13 +6397,13 @@
         <v>19</v>
       </c>
       <c r="B251" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C251" t="s">
         <v>27</v>
       </c>
       <c r="D251" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E251">
         <v>2</v>
@@ -6420,13 +6420,13 @@
         <v>20</v>
       </c>
       <c r="B252" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C252" t="s">
         <v>27</v>
       </c>
       <c r="D252" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E252">
         <v>8</v>
@@ -6443,13 +6443,13 @@
         <v>21</v>
       </c>
       <c r="B253" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C253" t="s">
         <v>27</v>
       </c>
       <c r="D253" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E253">
         <v>12</v>
@@ -6466,13 +6466,13 @@
         <v>4</v>
       </c>
       <c r="B254" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C254" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D254" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E254">
         <v>9</v>
@@ -6489,13 +6489,13 @@
         <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C255" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D255" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E255">
         <v>9</v>
@@ -6512,13 +6512,13 @@
         <v>6</v>
       </c>
       <c r="B256" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D256" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E256">
         <v>5</v>
@@ -6535,13 +6535,13 @@
         <v>7</v>
       </c>
       <c r="B257" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C257" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D257" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E257">
         <v>5</v>
@@ -6558,13 +6558,13 @@
         <v>8</v>
       </c>
       <c r="B258" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C258" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D258" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E258">
         <v>5</v>
@@ -6581,13 +6581,13 @@
         <v>9</v>
       </c>
       <c r="B259" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C259" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D259" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E259">
         <v>9</v>
@@ -6604,13 +6604,13 @@
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C260" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D260" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E260">
         <v>9</v>
@@ -6627,13 +6627,13 @@
         <v>11</v>
       </c>
       <c r="B261" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C261" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D261" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E261">
         <v>5</v>
@@ -6650,13 +6650,13 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C262" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D262" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E262">
         <v>5</v>
@@ -6673,13 +6673,13 @@
         <v>13</v>
       </c>
       <c r="B263" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C263" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D263" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E263">
         <v>5</v>
@@ -6696,13 +6696,13 @@
         <v>14</v>
       </c>
       <c r="B264" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C264" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D264" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E264">
         <v>9</v>
@@ -6719,13 +6719,13 @@
         <v>15</v>
       </c>
       <c r="B265" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C265" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D265" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E265">
         <v>8</v>
@@ -6742,13 +6742,13 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C266" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D266" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E266">
         <v>5</v>
@@ -6765,13 +6765,13 @@
         <v>17</v>
       </c>
       <c r="B267" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C267" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D267" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E267">
         <v>5</v>
@@ -6788,13 +6788,13 @@
         <v>18</v>
       </c>
       <c r="B268" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C268" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D268" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E268">
         <v>5</v>
@@ -6811,13 +6811,13 @@
         <v>19</v>
       </c>
       <c r="B269" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C269" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D269" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E269">
         <v>5</v>
@@ -6834,13 +6834,13 @@
         <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C270" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D270" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E270">
         <v>5</v>
@@ -6857,13 +6857,13 @@
         <v>21</v>
       </c>
       <c r="B271" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C271" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D271" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E271">
         <v>9</v>
@@ -6880,13 +6880,13 @@
         <v>4</v>
       </c>
       <c r="B272" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C272" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D272" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E272">
         <v>7</v>
@@ -6903,13 +6903,13 @@
         <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C273" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D273" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E273">
         <v>8</v>
@@ -6926,13 +6926,13 @@
         <v>6</v>
       </c>
       <c r="B274" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C274" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D274" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E274">
         <v>5</v>
@@ -6949,13 +6949,13 @@
         <v>7</v>
       </c>
       <c r="B275" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C275" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D275" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E275">
         <v>3</v>
@@ -6972,13 +6972,13 @@
         <v>8</v>
       </c>
       <c r="B276" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C276" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D276" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E276">
         <v>6</v>
@@ -6995,13 +6995,13 @@
         <v>9</v>
       </c>
       <c r="B277" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C277" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D277" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E277">
         <v>6</v>
@@ -7018,13 +7018,13 @@
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C278" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D278" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E278">
         <v>8</v>
@@ -7041,13 +7041,13 @@
         <v>11</v>
       </c>
       <c r="B279" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C279" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D279" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E279">
         <v>5</v>
@@ -7064,13 +7064,13 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C280" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D280" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E280">
         <v>5</v>
@@ -7087,13 +7087,13 @@
         <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C281" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D281" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E281">
         <v>6</v>
@@ -7110,13 +7110,13 @@
         <v>14</v>
       </c>
       <c r="B282" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C282" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D282" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E282">
         <v>6</v>
@@ -7133,13 +7133,13 @@
         <v>15</v>
       </c>
       <c r="B283" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C283" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D283" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E283">
         <v>3</v>
@@ -7156,13 +7156,13 @@
         <v>16</v>
       </c>
       <c r="B284" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C284" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D284" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E284">
         <v>5</v>
@@ -7179,13 +7179,13 @@
         <v>17</v>
       </c>
       <c r="B285" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C285" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D285" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E285">
         <v>7</v>
@@ -7202,13 +7202,13 @@
         <v>18</v>
       </c>
       <c r="B286" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C286" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D286" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E286">
         <v>7</v>
@@ -7225,13 +7225,13 @@
         <v>19</v>
       </c>
       <c r="B287" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C287" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D287" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E287">
         <v>5</v>
@@ -7248,13 +7248,13 @@
         <v>20</v>
       </c>
       <c r="B288" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C288" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D288" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E288">
         <v>6</v>
@@ -7271,13 +7271,13 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C289" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D289" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E289">
         <v>9</v>
@@ -7294,13 +7294,13 @@
         <v>4</v>
       </c>
       <c r="B290" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C290" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D290" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E290">
         <v>2</v>
@@ -7317,13 +7317,13 @@
         <v>5</v>
       </c>
       <c r="B291" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C291" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D291" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E291">
         <v>1</v>
@@ -7340,13 +7340,13 @@
         <v>6</v>
       </c>
       <c r="B292" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C292" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D292" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E292">
         <v>2</v>
@@ -7363,13 +7363,13 @@
         <v>7</v>
       </c>
       <c r="B293" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C293" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D293" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E293">
         <v>2</v>
@@ -7386,13 +7386,13 @@
         <v>8</v>
       </c>
       <c r="B294" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C294" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D294" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E294">
         <v>1</v>
@@ -7409,13 +7409,13 @@
         <v>9</v>
       </c>
       <c r="B295" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C295" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D295" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E295">
         <v>2</v>
@@ -7432,13 +7432,13 @@
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C296" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D296" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E296">
         <v>1</v>
@@ -7455,13 +7455,13 @@
         <v>11</v>
       </c>
       <c r="B297" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C297" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D297" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E297">
         <v>2</v>
@@ -7478,13 +7478,13 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C298" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D298" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E298">
         <v>2</v>
@@ -7501,13 +7501,13 @@
         <v>13</v>
       </c>
       <c r="B299" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C299" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D299" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E299">
         <v>2</v>
@@ -7524,13 +7524,13 @@
         <v>14</v>
       </c>
       <c r="B300" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C300" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D300" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E300">
         <v>2</v>
@@ -7547,13 +7547,13 @@
         <v>15</v>
       </c>
       <c r="B301" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C301" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D301" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E301">
         <v>1</v>
@@ -7570,13 +7570,13 @@
         <v>16</v>
       </c>
       <c r="B302" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C302" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D302" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E302">
         <v>2</v>
@@ -7593,13 +7593,13 @@
         <v>17</v>
       </c>
       <c r="B303" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C303" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D303" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E303">
         <v>1</v>
@@ -7616,13 +7616,13 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C304" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D304" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E304">
         <v>2</v>
@@ -7639,13 +7639,13 @@
         <v>19</v>
       </c>
       <c r="B305" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C305" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D305" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -7662,13 +7662,13 @@
         <v>20</v>
       </c>
       <c r="B306" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C306" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D306" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E306">
         <v>2</v>
@@ -7685,13 +7685,13 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C307" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D307" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E307">
         <v>2</v>
@@ -7708,13 +7708,13 @@
         <v>4</v>
       </c>
       <c r="B308" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C308" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D308" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -7731,13 +7731,13 @@
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C309" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D309" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E309">
         <v>1</v>
@@ -7754,13 +7754,13 @@
         <v>6</v>
       </c>
       <c r="B310" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C310" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D310" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -7777,13 +7777,13 @@
         <v>7</v>
       </c>
       <c r="B311" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C311" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D311" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -7800,13 +7800,13 @@
         <v>8</v>
       </c>
       <c r="B312" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C312" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D312" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -7823,13 +7823,13 @@
         <v>9</v>
       </c>
       <c r="B313" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C313" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D313" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E313">
         <v>1</v>
@@ -7846,13 +7846,13 @@
         <v>10</v>
       </c>
       <c r="B314" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C314" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D314" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E314">
         <v>1</v>
@@ -7869,13 +7869,13 @@
         <v>11</v>
       </c>
       <c r="B315" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C315" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D315" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E315">
         <v>0</v>
@@ -7892,13 +7892,13 @@
         <v>12</v>
       </c>
       <c r="B316" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C316" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D316" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -7915,13 +7915,13 @@
         <v>13</v>
       </c>
       <c r="B317" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C317" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D317" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -7938,13 +7938,13 @@
         <v>14</v>
       </c>
       <c r="B318" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C318" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D318" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E318">
         <v>1</v>
@@ -7961,13 +7961,13 @@
         <v>15</v>
       </c>
       <c r="B319" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C319" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D319" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>16</v>
       </c>
       <c r="B320" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C320" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D320" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -8007,13 +8007,13 @@
         <v>17</v>
       </c>
       <c r="B321" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C321" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D321" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -8030,13 +8030,13 @@
         <v>18</v>
       </c>
       <c r="B322" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C322" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D322" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -8053,13 +8053,13 @@
         <v>19</v>
       </c>
       <c r="B323" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C323" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D323" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -8076,13 +8076,13 @@
         <v>20</v>
       </c>
       <c r="B324" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C324" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D324" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -8099,13 +8099,13 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C325" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D325" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E325">
         <v>1</v>
@@ -8122,13 +8122,13 @@
         <v>4</v>
       </c>
       <c r="B326" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C326" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D326" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -8145,13 +8145,13 @@
         <v>5</v>
       </c>
       <c r="B327" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C327" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D327" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -8168,13 +8168,13 @@
         <v>6</v>
       </c>
       <c r="B328" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C328" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D328" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -8191,13 +8191,13 @@
         <v>7</v>
       </c>
       <c r="B329" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C329" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D329" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -8214,13 +8214,13 @@
         <v>8</v>
       </c>
       <c r="B330" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C330" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D330" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -8237,13 +8237,13 @@
         <v>9</v>
       </c>
       <c r="B331" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C331" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D331" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -8260,13 +8260,13 @@
         <v>10</v>
       </c>
       <c r="B332" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C332" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D332" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -8283,13 +8283,13 @@
         <v>11</v>
       </c>
       <c r="B333" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C333" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D333" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>12</v>
       </c>
       <c r="B334" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C334" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D334" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -8329,13 +8329,13 @@
         <v>13</v>
       </c>
       <c r="B335" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C335" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D335" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -8352,13 +8352,13 @@
         <v>14</v>
       </c>
       <c r="B336" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C336" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D336" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E336" s="1">
         <v>0</v>
@@ -8375,13 +8375,13 @@
         <v>15</v>
       </c>
       <c r="B337" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C337" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D337" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -8398,13 +8398,13 @@
         <v>16</v>
       </c>
       <c r="B338" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C338" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D338" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -8421,13 +8421,13 @@
         <v>17</v>
       </c>
       <c r="B339" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C339" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D339" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -8444,13 +8444,13 @@
         <v>18</v>
       </c>
       <c r="B340" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C340" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D340" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -8467,13 +8467,13 @@
         <v>19</v>
       </c>
       <c r="B341" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C341" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D341" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E341">
         <v>0</v>
@@ -8490,13 +8490,13 @@
         <v>20</v>
       </c>
       <c r="B342" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C342" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D342" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E342">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C343" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D343" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E343">
         <v>0</v>
@@ -8536,13 +8536,13 @@
         <v>4</v>
       </c>
       <c r="B344" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C344" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D344" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E344" s="1">
         <v>3</v>
@@ -8559,13 +8559,13 @@
         <v>5</v>
       </c>
       <c r="B345" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C345" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D345" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E345" s="1">
         <v>0</v>
@@ -8582,13 +8582,13 @@
         <v>6</v>
       </c>
       <c r="B346" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C346" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D346" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E346">
         <v>1</v>
@@ -8605,13 +8605,13 @@
         <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C347" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D347" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E347">
         <v>3</v>
@@ -8628,13 +8628,13 @@
         <v>8</v>
       </c>
       <c r="B348" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C348" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D348" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E348">
         <v>8.5</v>
@@ -8651,13 +8651,13 @@
         <v>9</v>
       </c>
       <c r="B349" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C349" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D349" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E349">
         <v>4</v>
@@ -8674,13 +8674,13 @@
         <v>10</v>
       </c>
       <c r="B350" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C350" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D350" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E350" s="1">
         <v>6</v>
@@ -8697,13 +8697,13 @@
         <v>11</v>
       </c>
       <c r="B351" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C351" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D351" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E351">
         <v>3</v>
@@ -8720,13 +8720,13 @@
         <v>12</v>
       </c>
       <c r="B352" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C352" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D352" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E352">
         <v>5</v>
@@ -8743,13 +8743,13 @@
         <v>13</v>
       </c>
       <c r="B353" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C353" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D353" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E353" s="1">
         <v>1</v>
@@ -8766,13 +8766,13 @@
         <v>14</v>
       </c>
       <c r="B354" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C354" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D354" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -8789,13 +8789,13 @@
         <v>15</v>
       </c>
       <c r="B355" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C355" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D355" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E355">
         <v>8.5</v>
@@ -8812,13 +8812,13 @@
         <v>16</v>
       </c>
       <c r="B356" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C356" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D356" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E356" s="1">
         <v>0</v>
@@ -8835,13 +8835,13 @@
         <v>17</v>
       </c>
       <c r="B357" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C357" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D357" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E357">
         <v>4</v>
@@ -8858,13 +8858,13 @@
         <v>18</v>
       </c>
       <c r="B358" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C358" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D358" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E358">
         <v>8</v>
@@ -8881,13 +8881,13 @@
         <v>19</v>
       </c>
       <c r="B359" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C359" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D359" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E359">
         <v>2</v>
@@ -8904,13 +8904,13 @@
         <v>20</v>
       </c>
       <c r="B360" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C360" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D360" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E360">
         <v>3</v>
@@ -8927,13 +8927,13 @@
         <v>21</v>
       </c>
       <c r="B361" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C361" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D361" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E361">
         <v>2</v>
@@ -8950,13 +8950,13 @@
         <v>4</v>
       </c>
       <c r="B362" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C362" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D362" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E362">
         <v>2</v>
@@ -8973,13 +8973,13 @@
         <v>5</v>
       </c>
       <c r="B363" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C363" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D363" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E363">
         <v>2.5</v>
@@ -8996,13 +8996,13 @@
         <v>6</v>
       </c>
       <c r="B364" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C364" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D364" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E364">
         <v>2</v>
@@ -9019,13 +9019,13 @@
         <v>7</v>
       </c>
       <c r="B365" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C365" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D365" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E365">
         <v>3</v>
@@ -9042,13 +9042,13 @@
         <v>8</v>
       </c>
       <c r="B366" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C366" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D366" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E366">
         <v>3.5</v>
@@ -9065,13 +9065,13 @@
         <v>9</v>
       </c>
       <c r="B367" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C367" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D367" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E367">
         <v>3</v>
@@ -9088,13 +9088,13 @@
         <v>10</v>
       </c>
       <c r="B368" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C368" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D368" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E368">
         <v>3</v>
@@ -9111,13 +9111,13 @@
         <v>11</v>
       </c>
       <c r="B369" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C369" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D369" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E369">
         <v>3</v>
@@ -9134,13 +9134,13 @@
         <v>12</v>
       </c>
       <c r="B370" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C370" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D370" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E370">
         <v>4</v>
@@ -9157,13 +9157,13 @@
         <v>13</v>
       </c>
       <c r="B371" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C371" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D371" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E371">
         <v>1</v>
@@ -9180,13 +9180,13 @@
         <v>14</v>
       </c>
       <c r="B372" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C372" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D372" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E372" s="1">
         <v>3</v>
@@ -9203,13 +9203,13 @@
         <v>15</v>
       </c>
       <c r="B373" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C373" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D373" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E373">
         <v>4</v>
@@ -9226,13 +9226,13 @@
         <v>16</v>
       </c>
       <c r="B374" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C374" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D374" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E374">
         <v>2</v>
@@ -9249,13 +9249,13 @@
         <v>17</v>
       </c>
       <c r="B375" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C375" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D375" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E375">
         <v>3</v>
@@ -9272,13 +9272,13 @@
         <v>18</v>
       </c>
       <c r="B376" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C376" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D376" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E376">
         <v>3.5</v>
@@ -9295,13 +9295,13 @@
         <v>19</v>
       </c>
       <c r="B377" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C377" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D377" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E377">
         <v>2</v>
@@ -9318,13 +9318,13 @@
         <v>20</v>
       </c>
       <c r="B378" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C378" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D378" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E378">
         <v>3</v>
@@ -9341,13 +9341,13 @@
         <v>21</v>
       </c>
       <c r="B379" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C379" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D379" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E379">
         <v>2.5</v>
@@ -9364,13 +9364,13 @@
         <v>4</v>
       </c>
       <c r="B380" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C380" t="s">
         <v>27</v>
       </c>
       <c r="D380" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E380">
         <v>0</v>
@@ -9387,13 +9387,13 @@
         <v>5</v>
       </c>
       <c r="B381" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C381" t="s">
         <v>27</v>
       </c>
       <c r="D381" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E381">
         <v>1</v>
@@ -9410,13 +9410,13 @@
         <v>6</v>
       </c>
       <c r="B382" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C382" t="s">
         <v>27</v>
       </c>
       <c r="D382" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E382">
         <v>1</v>
@@ -9433,13 +9433,13 @@
         <v>7</v>
       </c>
       <c r="B383" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C383" t="s">
         <v>27</v>
       </c>
       <c r="D383" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E383">
         <v>1.5</v>
@@ -9456,13 +9456,13 @@
         <v>8</v>
       </c>
       <c r="B384" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C384" t="s">
         <v>27</v>
       </c>
       <c r="D384" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E384">
         <v>2</v>
@@ -9479,13 +9479,13 @@
         <v>9</v>
       </c>
       <c r="B385" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C385" t="s">
         <v>27</v>
       </c>
       <c r="D385" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E385">
         <v>1.5</v>
@@ -9502,13 +9502,13 @@
         <v>10</v>
       </c>
       <c r="B386" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C386" t="s">
         <v>27</v>
       </c>
       <c r="D386" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E386">
         <v>1.5</v>
@@ -9525,13 +9525,13 @@
         <v>11</v>
       </c>
       <c r="B387" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C387" t="s">
         <v>27</v>
       </c>
       <c r="D387" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E387">
         <v>2</v>
@@ -9548,13 +9548,13 @@
         <v>12</v>
       </c>
       <c r="B388" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C388" t="s">
         <v>27</v>
       </c>
       <c r="D388" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E388">
         <v>3</v>
@@ -9571,13 +9571,13 @@
         <v>13</v>
       </c>
       <c r="B389" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C389" t="s">
         <v>27</v>
       </c>
       <c r="D389" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E389">
         <v>1</v>
@@ -9594,13 +9594,13 @@
         <v>14</v>
       </c>
       <c r="B390" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C390" t="s">
         <v>27</v>
       </c>
       <c r="D390" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E390" s="1">
         <v>1</v>
@@ -9617,13 +9617,13 @@
         <v>15</v>
       </c>
       <c r="B391" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C391" t="s">
         <v>27</v>
       </c>
       <c r="D391" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E391">
         <v>3</v>
@@ -9640,13 +9640,13 @@
         <v>16</v>
       </c>
       <c r="B392" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C392" t="s">
         <v>27</v>
       </c>
       <c r="D392" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E392">
         <v>2</v>
@@ -9663,13 +9663,13 @@
         <v>17</v>
       </c>
       <c r="B393" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C393" t="s">
         <v>27</v>
       </c>
       <c r="D393" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E393">
         <v>2</v>
@@ -9686,13 +9686,13 @@
         <v>18</v>
       </c>
       <c r="B394" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C394" t="s">
         <v>27</v>
       </c>
       <c r="D394" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E394">
         <v>2</v>
@@ -9709,13 +9709,13 @@
         <v>19</v>
       </c>
       <c r="B395" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C395" t="s">
         <v>27</v>
       </c>
       <c r="D395" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E395">
         <v>2</v>
@@ -9732,13 +9732,13 @@
         <v>20</v>
       </c>
       <c r="B396" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C396" t="s">
         <v>27</v>
       </c>
       <c r="D396" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E396">
         <v>1</v>
@@ -9755,13 +9755,13 @@
         <v>21</v>
       </c>
       <c r="B397" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C397" t="s">
         <v>27</v>
       </c>
       <c r="D397" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E397">
         <v>0</v>
@@ -9778,13 +9778,13 @@
         <v>4</v>
       </c>
       <c r="B398" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C398" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D398" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E398">
         <v>2</v>
@@ -9801,13 +9801,13 @@
         <v>5</v>
       </c>
       <c r="B399" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C399" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D399" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E399">
         <v>2</v>
@@ -9824,13 +9824,13 @@
         <v>6</v>
       </c>
       <c r="B400" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C400" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D400" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E400">
         <v>2</v>
@@ -9847,13 +9847,13 @@
         <v>7</v>
       </c>
       <c r="B401" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C401" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D401" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E401">
         <v>4</v>
@@ -9870,13 +9870,13 @@
         <v>8</v>
       </c>
       <c r="B402" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C402" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D402" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E402">
         <v>2</v>
@@ -9893,13 +9893,13 @@
         <v>9</v>
       </c>
       <c r="B403" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C403" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D403" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E403">
         <v>2</v>
@@ -9916,13 +9916,13 @@
         <v>10</v>
       </c>
       <c r="B404" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C404" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D404" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E404">
         <v>2</v>
@@ -9939,13 +9939,13 @@
         <v>11</v>
       </c>
       <c r="B405" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C405" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D405" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E405">
         <v>2</v>
@@ -9962,13 +9962,13 @@
         <v>12</v>
       </c>
       <c r="B406" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C406" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D406" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E406">
         <v>4</v>
@@ -9985,13 +9985,13 @@
         <v>13</v>
       </c>
       <c r="B407" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C407" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D407" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E407">
         <v>2</v>
@@ -10008,13 +10008,13 @@
         <v>14</v>
       </c>
       <c r="B408" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C408" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D408" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E408" s="1">
         <v>2</v>
@@ -10031,13 +10031,13 @@
         <v>15</v>
       </c>
       <c r="B409" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C409" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D409" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E409">
         <v>4</v>
@@ -10054,13 +10054,13 @@
         <v>16</v>
       </c>
       <c r="B410" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C410" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D410" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E410">
         <v>2</v>
@@ -10077,13 +10077,13 @@
         <v>17</v>
       </c>
       <c r="B411" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C411" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D411" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E411">
         <v>4</v>
@@ -10100,13 +10100,13 @@
         <v>18</v>
       </c>
       <c r="B412" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C412" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D412" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E412">
         <v>4</v>
@@ -10123,13 +10123,13 @@
         <v>19</v>
       </c>
       <c r="B413" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C413" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D413" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E413">
         <v>2</v>
@@ -10146,13 +10146,13 @@
         <v>20</v>
       </c>
       <c r="B414" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C414" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D414" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E414">
         <v>4</v>
@@ -10169,13 +10169,13 @@
         <v>21</v>
       </c>
       <c r="B415" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C415" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D415" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E415">
         <v>1</v>
@@ -10192,13 +10192,13 @@
         <v>4</v>
       </c>
       <c r="B416" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C416" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D416" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E416">
         <v>1</v>
@@ -10215,13 +10215,13 @@
         <v>5</v>
       </c>
       <c r="B417" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C417" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D417" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E417">
         <v>1</v>
@@ -10238,13 +10238,13 @@
         <v>6</v>
       </c>
       <c r="B418" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C418" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D418" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E418">
         <v>1</v>
@@ -10261,13 +10261,13 @@
         <v>7</v>
       </c>
       <c r="B419" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C419" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D419" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E419">
         <v>1</v>
@@ -10284,13 +10284,13 @@
         <v>8</v>
       </c>
       <c r="B420" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C420" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D420" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E420">
         <v>1</v>
@@ -10307,13 +10307,13 @@
         <v>9</v>
       </c>
       <c r="B421" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C421" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D421" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E421">
         <v>1</v>
@@ -10330,13 +10330,13 @@
         <v>10</v>
       </c>
       <c r="B422" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C422" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D422" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E422">
         <v>1</v>
@@ -10353,13 +10353,13 @@
         <v>11</v>
       </c>
       <c r="B423" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C423" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D423" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E423">
         <v>1</v>
@@ -10376,13 +10376,13 @@
         <v>12</v>
       </c>
       <c r="B424" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C424" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D424" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E424">
         <v>1</v>
@@ -10399,13 +10399,13 @@
         <v>13</v>
       </c>
       <c r="B425" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C425" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D425" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E425">
         <v>0</v>
@@ -10422,13 +10422,13 @@
         <v>14</v>
       </c>
       <c r="B426" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C426" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D426" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E426" s="1">
         <v>1</v>
@@ -10445,13 +10445,13 @@
         <v>15</v>
       </c>
       <c r="B427" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C427" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D427" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E427">
         <v>1</v>
@@ -10468,13 +10468,13 @@
         <v>16</v>
       </c>
       <c r="B428" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C428" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D428" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E428">
         <v>1</v>
@@ -10491,13 +10491,13 @@
         <v>17</v>
       </c>
       <c r="B429" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C429" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D429" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E429">
         <v>1</v>
@@ -10514,13 +10514,13 @@
         <v>18</v>
       </c>
       <c r="B430" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C430" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D430" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E430">
         <v>1</v>
@@ -10537,13 +10537,13 @@
         <v>19</v>
       </c>
       <c r="B431" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C431" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D431" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E431">
         <v>1</v>
@@ -10560,13 +10560,13 @@
         <v>20</v>
       </c>
       <c r="B432" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C432" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D432" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E432">
         <v>1</v>
@@ -10583,13 +10583,13 @@
         <v>21</v>
       </c>
       <c r="B433" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C433" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D433" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E433">
         <v>0</v>
@@ -10606,13 +10606,13 @@
         <v>4</v>
       </c>
       <c r="B434" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C434" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D434" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E434">
         <v>3.5</v>
@@ -10629,13 +10629,13 @@
         <v>5</v>
       </c>
       <c r="B435" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C435" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D435" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E435" s="1">
         <v>3.5</v>
@@ -10652,13 +10652,13 @@
         <v>6</v>
       </c>
       <c r="B436" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C436" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D436" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E436" s="1">
         <v>2</v>
@@ -10675,13 +10675,13 @@
         <v>7</v>
       </c>
       <c r="B437" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C437" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D437" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E437" s="1">
         <v>6</v>
@@ -10698,13 +10698,13 @@
         <v>8</v>
       </c>
       <c r="B438" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C438" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D438" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E438" s="1">
         <v>11.5</v>
@@ -10721,13 +10721,13 @@
         <v>9</v>
       </c>
       <c r="B439" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C439" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D439" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E439" s="1">
         <v>4</v>
@@ -10744,13 +10744,13 @@
         <v>10</v>
       </c>
       <c r="B440" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C440" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D440" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E440">
         <v>9</v>
@@ -10767,13 +10767,13 @@
         <v>11</v>
       </c>
       <c r="B441" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C441" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D441" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E441" s="1">
         <v>5.5</v>
@@ -10790,13 +10790,13 @@
         <v>12</v>
       </c>
       <c r="B442" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C442" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D442" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E442" s="1">
         <v>8</v>
@@ -10813,13 +10813,13 @@
         <v>13</v>
       </c>
       <c r="B443" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C443" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D443" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E443">
         <v>2</v>
@@ -10836,13 +10836,13 @@
         <v>14</v>
       </c>
       <c r="B444" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C444" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D444" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E444" s="1">
         <v>3</v>
@@ -10859,13 +10859,13 @@
         <v>15</v>
       </c>
       <c r="B445" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C445" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D445" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E445" s="1">
         <v>12.5</v>
@@ -10882,13 +10882,13 @@
         <v>16</v>
       </c>
       <c r="B446" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C446" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D446" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E446">
         <v>2</v>
@@ -10905,13 +10905,13 @@
         <v>17</v>
       </c>
       <c r="B447" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C447" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D447" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E447">
         <v>5</v>
@@ -10928,13 +10928,13 @@
         <v>18</v>
       </c>
       <c r="B448" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C448" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D448" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E448" s="1">
         <v>8</v>
@@ -10951,13 +10951,13 @@
         <v>19</v>
       </c>
       <c r="B449" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C449" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D449" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E449" s="1">
         <v>2.5</v>
@@ -10974,13 +10974,13 @@
         <v>20</v>
       </c>
       <c r="B450" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C450" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D450" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E450">
         <v>2.5</v>
@@ -10997,13 +10997,13 @@
         <v>21</v>
       </c>
       <c r="B451" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C451" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D451" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E451">
         <v>12</v>
@@ -11034,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -11045,13 +11045,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -11059,13 +11059,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -11073,10 +11073,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -11084,32 +11084,32 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/phi_data_combined.xlsx
+++ b/data/phi_data_combined.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolinkilian/Desktop/Public Health Index/Github/Public-Health-Index/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6892E899-9132-2F45-BE74-C9E4B3C1B0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43969CEA-610D-3B48-9BD0-2167A2D99958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39820" yWindow="8600" windowWidth="27340" windowHeight="20980" xr2:uid="{07406E1C-1769-574D-9B9C-B78BFD08E78B}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" xr2:uid="{07406E1C-1769-574D-9B9C-B78BFD08E78B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="codebook" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$451</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$469</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="72">
   <si>
     <t>country</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>social and living environmental controls</t>
+  </si>
+  <si>
+    <t>fctc</t>
   </si>
 </sst>
 </file>
@@ -639,7 +642,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55F2ECBD-B66B-9E43-893D-B37A0B73B8F5}">
-  <dimension ref="A1:G451"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G469"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -665,7 +669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -688,7 +692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -711,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -734,7 +738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -757,7 +761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -780,7 +784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -803,7 +807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -826,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -849,7 +853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -872,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -895,7 +899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -918,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -941,7 +945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -964,7 +968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -987,7 +991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1033,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1056,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1079,7 +1083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1102,7 +1106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1125,7 +1129,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1148,7 +1152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1171,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -1194,7 +1198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1217,7 +1221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1240,7 +1244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1263,7 +1267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1286,7 +1290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1309,7 +1313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -1332,7 +1336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1378,7 +1382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1401,7 +1405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -1424,7 +1428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -1447,7 +1451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -1470,7 +1474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1516,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1539,7 +1543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1562,7 +1566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1585,7 +1589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1608,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -1631,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -1654,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -1677,7 +1681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -1723,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -1746,7 +1750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -1769,7 +1773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>16</v>
       </c>
@@ -1792,7 +1796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -1815,7 +1819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -1838,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>19</v>
       </c>
@@ -1861,7 +1865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>20</v>
       </c>
@@ -1884,7 +1888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>21</v>
       </c>
@@ -1907,7 +1911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1930,7 +1934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -1953,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1976,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -1999,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -2022,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -2045,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>10</v>
       </c>
@@ -2068,7 +2072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -2091,7 +2095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -2114,7 +2118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -2137,7 +2141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -2160,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>15</v>
       </c>
@@ -2183,7 +2187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>16</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2229,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -2252,7 +2256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -2275,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -2298,7 +2302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -2321,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -2367,7 +2371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2390,7 +2394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>7</v>
       </c>
@@ -2413,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -2436,7 +2440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2459,7 +2463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>10</v>
       </c>
@@ -2482,7 +2486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2505,7 +2509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -2528,7 +2532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>13</v>
       </c>
@@ -2551,7 +2555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -2574,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -2597,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -2620,7 +2624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -2643,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -2666,7 +2670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>19</v>
       </c>
@@ -2689,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -2712,7 +2716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>21</v>
       </c>
@@ -2735,7 +2739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2758,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -2781,7 +2785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -2827,7 +2831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -2850,7 +2854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2873,7 +2877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>10</v>
       </c>
@@ -2896,7 +2900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2919,7 +2923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>12</v>
       </c>
@@ -2942,7 +2946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -2965,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>14</v>
       </c>
@@ -2988,7 +2992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -3011,7 +3015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -3034,7 +3038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -3057,7 +3061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -3080,7 +3084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -3103,7 +3107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>20</v>
       </c>
@@ -3126,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>21</v>
       </c>
@@ -4221,7 +4225,7 @@
         <v>33</v>
       </c>
       <c r="E156">
-        <v>0.2278</v>
+        <v>0.27779999999999999</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -4805,7 +4809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>4</v>
       </c>
@@ -4828,7 +4832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -4851,7 +4855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>6</v>
       </c>
@@ -4874,7 +4878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>7</v>
       </c>
@@ -4897,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>8</v>
       </c>
@@ -4920,7 +4924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -4943,7 +4947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -4966,7 +4970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -4989,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -5012,7 +5016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -5035,7 +5039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>14</v>
       </c>
@@ -5058,7 +5062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>15</v>
       </c>
@@ -5081,7 +5085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -5104,7 +5108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -5127,7 +5131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -5150,7 +5154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>19</v>
       </c>
@@ -5173,7 +5177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>20</v>
       </c>
@@ -5196,7 +5200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>21</v>
       </c>
@@ -5219,7 +5223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>4</v>
       </c>
@@ -5242,7 +5246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -5265,7 +5269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -5288,7 +5292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>7</v>
       </c>
@@ -5311,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>8</v>
       </c>
@@ -5334,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -5380,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>11</v>
       </c>
@@ -5403,7 +5407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>12</v>
       </c>
@@ -5426,7 +5430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>14</v>
       </c>
@@ -5472,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>15</v>
       </c>
@@ -5495,7 +5499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -5518,7 +5522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>17</v>
       </c>
@@ -5541,7 +5545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -5564,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>19</v>
       </c>
@@ -5587,7 +5591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>20</v>
       </c>
@@ -5610,7 +5614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>21</v>
       </c>
@@ -5633,7 +5637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>4</v>
       </c>
@@ -5656,7 +5660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -5679,7 +5683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -5702,7 +5706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>7</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>8</v>
       </c>
@@ -5748,7 +5752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -5771,7 +5775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>10</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>11</v>
       </c>
@@ -5817,7 +5821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>12</v>
       </c>
@@ -5840,7 +5844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>13</v>
       </c>
@@ -5863,7 +5867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -5886,7 +5890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>15</v>
       </c>
@@ -5909,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -5932,7 +5936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>17</v>
       </c>
@@ -5955,7 +5959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -5978,7 +5982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>19</v>
       </c>
@@ -6001,7 +6005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>20</v>
       </c>
@@ -6024,7 +6028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>21</v>
       </c>
@@ -6047,7 +6051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>4</v>
       </c>
@@ -6070,7 +6074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -6093,7 +6097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>6</v>
       </c>
@@ -6116,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>7</v>
       </c>
@@ -6139,7 +6143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>8</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>9</v>
       </c>
@@ -6185,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -6208,7 +6212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>11</v>
       </c>
@@ -6231,7 +6235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>12</v>
       </c>
@@ -6254,7 +6258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -6277,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>15</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -6346,7 +6350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -6369,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -6392,7 +6396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>19</v>
       </c>
@@ -6415,7 +6419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>20</v>
       </c>
@@ -6438,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>21</v>
       </c>
@@ -6461,7 +6465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>4</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>5</v>
       </c>
@@ -6507,7 +6511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>6</v>
       </c>
@@ -6530,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>7</v>
       </c>
@@ -6553,7 +6557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>8</v>
       </c>
@@ -6576,7 +6580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>9</v>
       </c>
@@ -6599,7 +6603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -6622,7 +6626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -6645,7 +6649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>12</v>
       </c>
@@ -6668,7 +6672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>13</v>
       </c>
@@ -6691,7 +6695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>14</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>15</v>
       </c>
@@ -6737,7 +6741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -6760,7 +6764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>17</v>
       </c>
@@ -6783,7 +6787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -6806,7 +6810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>19</v>
       </c>
@@ -6829,7 +6833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>20</v>
       </c>
@@ -6852,7 +6856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>21</v>
       </c>
@@ -6875,7 +6879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>4</v>
       </c>
@@ -6898,7 +6902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -6921,7 +6925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -6967,7 +6971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>8</v>
       </c>
@@ -6990,7 +6994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>9</v>
       </c>
@@ -7013,7 +7017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>10</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>11</v>
       </c>
@@ -7059,7 +7063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>12</v>
       </c>
@@ -7082,7 +7086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>13</v>
       </c>
@@ -7105,7 +7109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>14</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>15</v>
       </c>
@@ -7151,7 +7155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -7174,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>17</v>
       </c>
@@ -7197,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -7220,7 +7224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>19</v>
       </c>
@@ -7243,7 +7247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>20</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>21</v>
       </c>
@@ -7289,7 +7293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>4</v>
       </c>
@@ -7312,7 +7316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>5</v>
       </c>
@@ -7335,7 +7339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>6</v>
       </c>
@@ -7358,7 +7362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>7</v>
       </c>
@@ -7381,7 +7385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>8</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>9</v>
       </c>
@@ -7427,7 +7431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>10</v>
       </c>
@@ -7450,7 +7454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>11</v>
       </c>
@@ -7473,7 +7477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>12</v>
       </c>
@@ -7496,7 +7500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>13</v>
       </c>
@@ -7519,7 +7523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>14</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>15</v>
       </c>
@@ -7565,7 +7569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -7588,7 +7592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -7611,7 +7615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>18</v>
       </c>
@@ -7634,7 +7638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>19</v>
       </c>
@@ -7657,7 +7661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>20</v>
       </c>
@@ -7680,7 +7684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>21</v>
       </c>
@@ -7703,7 +7707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>4</v>
       </c>
@@ -7726,7 +7730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>5</v>
       </c>
@@ -7749,7 +7753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>6</v>
       </c>
@@ -7772,7 +7776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>7</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>8</v>
       </c>
@@ -7818,7 +7822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>9</v>
       </c>
@@ -7841,7 +7845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>10</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>11</v>
       </c>
@@ -7887,7 +7891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>12</v>
       </c>
@@ -7910,7 +7914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>13</v>
       </c>
@@ -7933,7 +7937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>14</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>15</v>
       </c>
@@ -7979,7 +7983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>17</v>
       </c>
@@ -8025,7 +8029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>18</v>
       </c>
@@ -8048,7 +8052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>19</v>
       </c>
@@ -8071,7 +8075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>20</v>
       </c>
@@ -8094,7 +8098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>21</v>
       </c>
@@ -8117,7 +8121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>4</v>
       </c>
@@ -8140,7 +8144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>5</v>
       </c>
@@ -8163,7 +8167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -8186,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>7</v>
       </c>
@@ -8209,7 +8213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>8</v>
       </c>
@@ -8232,7 +8236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>9</v>
       </c>
@@ -8255,7 +8259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>10</v>
       </c>
@@ -8278,7 +8282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>11</v>
       </c>
@@ -8301,7 +8305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>12</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>13</v>
       </c>
@@ -8347,7 +8351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>14</v>
       </c>
@@ -8370,7 +8374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>15</v>
       </c>
@@ -8393,7 +8397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>16</v>
       </c>
@@ -8416,7 +8420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>17</v>
       </c>
@@ -8439,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>18</v>
       </c>
@@ -8462,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>19</v>
       </c>
@@ -8485,7 +8489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>20</v>
       </c>
@@ -8508,7 +8512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>21</v>
       </c>
@@ -8531,7 +8535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>4</v>
       </c>
@@ -8554,7 +8558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -8577,7 +8581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -8600,7 +8604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>7</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>8</v>
       </c>
@@ -8646,7 +8650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>9</v>
       </c>
@@ -8669,7 +8673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>10</v>
       </c>
@@ -8692,7 +8696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>11</v>
       </c>
@@ -8715,7 +8719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>12</v>
       </c>
@@ -8738,7 +8742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>13</v>
       </c>
@@ -8761,7 +8765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>14</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>15</v>
       </c>
@@ -8807,7 +8811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>16</v>
       </c>
@@ -8830,7 +8834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -8853,7 +8857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>18</v>
       </c>
@@ -8876,7 +8880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>19</v>
       </c>
@@ -8899,7 +8903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>20</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>21</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>4</v>
       </c>
@@ -8968,7 +8972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -8991,7 +8995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>7</v>
       </c>
@@ -9037,7 +9041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>8</v>
       </c>
@@ -9060,7 +9064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>9</v>
       </c>
@@ -9083,7 +9087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>10</v>
       </c>
@@ -9106,7 +9110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>11</v>
       </c>
@@ -9129,7 +9133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>12</v>
       </c>
@@ -9152,7 +9156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>13</v>
       </c>
@@ -9175,7 +9179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>14</v>
       </c>
@@ -9198,7 +9202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>15</v>
       </c>
@@ -9221,7 +9225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>16</v>
       </c>
@@ -9244,7 +9248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>17</v>
       </c>
@@ -9267,7 +9271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>18</v>
       </c>
@@ -9290,7 +9294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>19</v>
       </c>
@@ -9313,7 +9317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>20</v>
       </c>
@@ -9336,7 +9340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>21</v>
       </c>
@@ -9359,7 +9363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>4</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>5</v>
       </c>
@@ -9405,7 +9409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>6</v>
       </c>
@@ -9428,7 +9432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>7</v>
       </c>
@@ -9451,7 +9455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>8</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>9</v>
       </c>
@@ -9497,7 +9501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>10</v>
       </c>
@@ -9520,7 +9524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>11</v>
       </c>
@@ -9543,7 +9547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>12</v>
       </c>
@@ -9566,7 +9570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>13</v>
       </c>
@@ -9589,7 +9593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>14</v>
       </c>
@@ -9612,7 +9616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>15</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>16</v>
       </c>
@@ -9658,7 +9662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>17</v>
       </c>
@@ -9681,7 +9685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>18</v>
       </c>
@@ -9704,7 +9708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>19</v>
       </c>
@@ -9727,7 +9731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>20</v>
       </c>
@@ -9750,7 +9754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>21</v>
       </c>
@@ -9773,7 +9777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>4</v>
       </c>
@@ -9796,7 +9800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>5</v>
       </c>
@@ -9819,7 +9823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>6</v>
       </c>
@@ -9842,7 +9846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>7</v>
       </c>
@@ -9865,7 +9869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>8</v>
       </c>
@@ -9888,7 +9892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>9</v>
       </c>
@@ -9911,7 +9915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>10</v>
       </c>
@@ -9934,7 +9938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>11</v>
       </c>
@@ -9957,7 +9961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>12</v>
       </c>
@@ -9980,7 +9984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>13</v>
       </c>
@@ -10003,7 +10007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>14</v>
       </c>
@@ -10026,7 +10030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>15</v>
       </c>
@@ -10049,7 +10053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>16</v>
       </c>
@@ -10072,7 +10076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>17</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>18</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>19</v>
       </c>
@@ -10141,7 +10145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>20</v>
       </c>
@@ -10164,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>21</v>
       </c>
@@ -10187,7 +10191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>4</v>
       </c>
@@ -10210,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>5</v>
       </c>
@@ -10233,7 +10237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>6</v>
       </c>
@@ -10256,7 +10260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>7</v>
       </c>
@@ -10279,7 +10283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>8</v>
       </c>
@@ -10302,7 +10306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>9</v>
       </c>
@@ -10325,7 +10329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>10</v>
       </c>
@@ -10348,7 +10352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>11</v>
       </c>
@@ -10371,7 +10375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>12</v>
       </c>
@@ -10394,7 +10398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>13</v>
       </c>
@@ -10417,7 +10421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>14</v>
       </c>
@@ -10440,7 +10444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>15</v>
       </c>
@@ -10463,7 +10467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>16</v>
       </c>
@@ -10486,7 +10490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -10509,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>18</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>19</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>20</v>
       </c>
@@ -10578,7 +10582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>21</v>
       </c>
@@ -10601,7 +10605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>4</v>
       </c>
@@ -10624,7 +10628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -10647,7 +10651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -10670,7 +10674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>7</v>
       </c>
@@ -10693,7 +10697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>8</v>
       </c>
@@ -10716,7 +10720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>9</v>
       </c>
@@ -10739,7 +10743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>10</v>
       </c>
@@ -10762,7 +10766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>11</v>
       </c>
@@ -10785,7 +10789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>12</v>
       </c>
@@ -10808,7 +10812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>13</v>
       </c>
@@ -10831,7 +10835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>14</v>
       </c>
@@ -10854,7 +10858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>15</v>
       </c>
@@ -10877,7 +10881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>16</v>
       </c>
@@ -10900,7 +10904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>17</v>
       </c>
@@ -10923,7 +10927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>18</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -10969,7 +10973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>20</v>
       </c>
@@ -10992,7 +10996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>21</v>
       </c>
@@ -11015,8 +11019,428 @@
         <v>1</v>
       </c>
     </row>
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>4</v>
+      </c>
+      <c r="B452" t="s">
+        <v>36</v>
+      </c>
+      <c r="C452" t="s">
+        <v>37</v>
+      </c>
+      <c r="D452" t="s">
+        <v>71</v>
+      </c>
+      <c r="E452">
+        <v>0</v>
+      </c>
+      <c r="F452">
+        <v>0</v>
+      </c>
+      <c r="G452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>5</v>
+      </c>
+      <c r="B453" t="s">
+        <v>36</v>
+      </c>
+      <c r="C453" t="s">
+        <v>37</v>
+      </c>
+      <c r="D453" t="s">
+        <v>71</v>
+      </c>
+      <c r="E453">
+        <v>0</v>
+      </c>
+      <c r="F453">
+        <v>0</v>
+      </c>
+      <c r="G453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>6</v>
+      </c>
+      <c r="B454" t="s">
+        <v>36</v>
+      </c>
+      <c r="C454" t="s">
+        <v>37</v>
+      </c>
+      <c r="D454" t="s">
+        <v>71</v>
+      </c>
+      <c r="E454">
+        <v>0</v>
+      </c>
+      <c r="F454">
+        <v>0</v>
+      </c>
+      <c r="G454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>7</v>
+      </c>
+      <c r="B455" t="s">
+        <v>36</v>
+      </c>
+      <c r="C455" t="s">
+        <v>37</v>
+      </c>
+      <c r="D455" t="s">
+        <v>71</v>
+      </c>
+      <c r="E455">
+        <v>0</v>
+      </c>
+      <c r="F455">
+        <v>0</v>
+      </c>
+      <c r="G455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>8</v>
+      </c>
+      <c r="B456" t="s">
+        <v>36</v>
+      </c>
+      <c r="C456" t="s">
+        <v>37</v>
+      </c>
+      <c r="D456" t="s">
+        <v>71</v>
+      </c>
+      <c r="E456">
+        <v>0</v>
+      </c>
+      <c r="F456">
+        <v>0</v>
+      </c>
+      <c r="G456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>9</v>
+      </c>
+      <c r="B457" t="s">
+        <v>36</v>
+      </c>
+      <c r="C457" t="s">
+        <v>37</v>
+      </c>
+      <c r="D457" t="s">
+        <v>71</v>
+      </c>
+      <c r="E457">
+        <v>0</v>
+      </c>
+      <c r="F457">
+        <v>0</v>
+      </c>
+      <c r="G457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>10</v>
+      </c>
+      <c r="B458" t="s">
+        <v>36</v>
+      </c>
+      <c r="C458" t="s">
+        <v>37</v>
+      </c>
+      <c r="D458" t="s">
+        <v>71</v>
+      </c>
+      <c r="E458">
+        <v>0</v>
+      </c>
+      <c r="F458">
+        <v>0</v>
+      </c>
+      <c r="G458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>11</v>
+      </c>
+      <c r="B459" t="s">
+        <v>36</v>
+      </c>
+      <c r="C459" t="s">
+        <v>37</v>
+      </c>
+      <c r="D459" t="s">
+        <v>71</v>
+      </c>
+      <c r="E459">
+        <v>0</v>
+      </c>
+      <c r="F459">
+        <v>0</v>
+      </c>
+      <c r="G459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>12</v>
+      </c>
+      <c r="B460" t="s">
+        <v>36</v>
+      </c>
+      <c r="C460" t="s">
+        <v>37</v>
+      </c>
+      <c r="D460" t="s">
+        <v>71</v>
+      </c>
+      <c r="E460">
+        <v>0</v>
+      </c>
+      <c r="F460">
+        <v>0</v>
+      </c>
+      <c r="G460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>13</v>
+      </c>
+      <c r="B461" t="s">
+        <v>36</v>
+      </c>
+      <c r="C461" t="s">
+        <v>37</v>
+      </c>
+      <c r="D461" t="s">
+        <v>71</v>
+      </c>
+      <c r="E461">
+        <v>0</v>
+      </c>
+      <c r="F461">
+        <v>0</v>
+      </c>
+      <c r="G461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>14</v>
+      </c>
+      <c r="B462" t="s">
+        <v>36</v>
+      </c>
+      <c r="C462" t="s">
+        <v>37</v>
+      </c>
+      <c r="D462" t="s">
+        <v>71</v>
+      </c>
+      <c r="E462">
+        <v>0</v>
+      </c>
+      <c r="F462">
+        <v>0</v>
+      </c>
+      <c r="G462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>15</v>
+      </c>
+      <c r="B463" t="s">
+        <v>36</v>
+      </c>
+      <c r="C463" t="s">
+        <v>37</v>
+      </c>
+      <c r="D463" t="s">
+        <v>71</v>
+      </c>
+      <c r="E463">
+        <v>0</v>
+      </c>
+      <c r="F463">
+        <v>0</v>
+      </c>
+      <c r="G463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>16</v>
+      </c>
+      <c r="B464" t="s">
+        <v>36</v>
+      </c>
+      <c r="C464" t="s">
+        <v>37</v>
+      </c>
+      <c r="D464" t="s">
+        <v>71</v>
+      </c>
+      <c r="E464">
+        <v>0</v>
+      </c>
+      <c r="F464">
+        <v>0</v>
+      </c>
+      <c r="G464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>17</v>
+      </c>
+      <c r="B465" t="s">
+        <v>36</v>
+      </c>
+      <c r="C465" t="s">
+        <v>37</v>
+      </c>
+      <c r="D465" t="s">
+        <v>71</v>
+      </c>
+      <c r="E465">
+        <v>0</v>
+      </c>
+      <c r="F465">
+        <v>0</v>
+      </c>
+      <c r="G465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>18</v>
+      </c>
+      <c r="B466" t="s">
+        <v>36</v>
+      </c>
+      <c r="C466" t="s">
+        <v>37</v>
+      </c>
+      <c r="D466" t="s">
+        <v>71</v>
+      </c>
+      <c r="E466">
+        <v>0</v>
+      </c>
+      <c r="F466">
+        <v>0</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>19</v>
+      </c>
+      <c r="B467" t="s">
+        <v>36</v>
+      </c>
+      <c r="C467" t="s">
+        <v>37</v>
+      </c>
+      <c r="D467" t="s">
+        <v>71</v>
+      </c>
+      <c r="E467">
+        <v>-1</v>
+      </c>
+      <c r="F467">
+        <v>0</v>
+      </c>
+      <c r="G467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>20</v>
+      </c>
+      <c r="B468" t="s">
+        <v>36</v>
+      </c>
+      <c r="C468" t="s">
+        <v>37</v>
+      </c>
+      <c r="D468" t="s">
+        <v>71</v>
+      </c>
+      <c r="E468">
+        <v>0</v>
+      </c>
+      <c r="F468">
+        <v>0</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>21</v>
+      </c>
+      <c r="B469" t="s">
+        <v>36</v>
+      </c>
+      <c r="C469" t="s">
+        <v>37</v>
+      </c>
+      <c r="D469" t="s">
+        <v>71</v>
+      </c>
+      <c r="E469">
+        <v>0</v>
+      </c>
+      <c r="F469">
+        <v>0</v>
+      </c>
+      <c r="G469">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G451" xr:uid="{55F2ECBD-B66B-9E43-893D-B37A0B73B8F5}"/>
+  <autoFilter ref="A1:G469" xr:uid="{55F2ECBD-B66B-9E43-893D-B37A0B73B8F5}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Physical activity"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/phi_data_combined.xlsx
+++ b/data/phi_data_combined.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carolinkilian/Desktop/Research projects/Public Health Index/Github/Public-Health-Index/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B811D35-B7F3-374E-858E-2B0091F3559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E3CA47-6DBE-7C40-BC12-766826A8D584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{07406E1C-1769-574D-9B9C-B78BFD08E78B}"/>
   </bookViews>
@@ -3991,7 +3991,7 @@
         <v>72</v>
       </c>
       <c r="C146" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D146" t="s">
         <v>31</v>
@@ -4014,7 +4014,7 @@
         <v>72</v>
       </c>
       <c r="C147" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D147" t="s">
         <v>31</v>
@@ -4037,7 +4037,7 @@
         <v>72</v>
       </c>
       <c r="C148" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D148" t="s">
         <v>31</v>
@@ -4060,7 +4060,7 @@
         <v>72</v>
       </c>
       <c r="C149" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D149" t="s">
         <v>31</v>
@@ -4083,7 +4083,7 @@
         <v>72</v>
       </c>
       <c r="C150" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D150" t="s">
         <v>31</v>
@@ -4106,7 +4106,7 @@
         <v>72</v>
       </c>
       <c r="C151" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D151" t="s">
         <v>31</v>
@@ -4129,7 +4129,7 @@
         <v>72</v>
       </c>
       <c r="C152" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D152" t="s">
         <v>31</v>
@@ -4152,7 +4152,7 @@
         <v>72</v>
       </c>
       <c r="C153" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D153" t="s">
         <v>31</v>
@@ -4175,7 +4175,7 @@
         <v>72</v>
       </c>
       <c r="C154" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D154" t="s">
         <v>31</v>
@@ -4198,7 +4198,7 @@
         <v>72</v>
       </c>
       <c r="C155" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D155" t="s">
         <v>31</v>
@@ -4221,7 +4221,7 @@
         <v>72</v>
       </c>
       <c r="C156" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D156" t="s">
         <v>31</v>
@@ -4244,7 +4244,7 @@
         <v>72</v>
       </c>
       <c r="C157" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D157" t="s">
         <v>31</v>
@@ -4267,7 +4267,7 @@
         <v>72</v>
       </c>
       <c r="C158" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D158" t="s">
         <v>31</v>
@@ -4290,7 +4290,7 @@
         <v>72</v>
       </c>
       <c r="C159" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D159" t="s">
         <v>31</v>
@@ -4313,7 +4313,7 @@
         <v>72</v>
       </c>
       <c r="C160" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D160" t="s">
         <v>31</v>
@@ -4336,7 +4336,7 @@
         <v>72</v>
       </c>
       <c r="C161" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D161" t="s">
         <v>31</v>
@@ -4359,7 +4359,7 @@
         <v>72</v>
       </c>
       <c r="C162" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D162" t="s">
         <v>31</v>
@@ -4382,7 +4382,7 @@
         <v>72</v>
       </c>
       <c r="C163" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D163" t="s">
         <v>31</v>
